--- a/hourly datasets/cap_gen_year8final.xlsx
+++ b/hourly datasets/cap_gen_year8final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09433620093527373</v>
+        <v>0.09223107840310137</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1029574324638085</v>
+        <v>0.09877494058704042</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1972936333990822</v>
+        <v>0.1910060189901418</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08409957213983206</v>
+        <v>0.08041191303485394</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1784357730751058</v>
+        <v>0.1726429914379553</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06457353709297113</v>
+        <v>0.05721070602727303</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1589097380282449</v>
+        <v>0.1494417844303744</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04573420860271862</v>
+        <v>0.03592349993804324</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +557,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1400704095379924</v>
+        <v>0.1281545783411446</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02323290200375484</v>
+        <v>0.01128458280286472</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002508239712143095</v>
+        <v>0.001106705717181267</v>
       </c>
       <c r="D7" t="n">
-        <v>3.018807889841133</v>
+        <v>2.359853202451919</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0137343863590084</v>
+        <v>0.01112575066180846</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01830203432820247</v>
+        <v>0.009114094713539968</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02816376967930696</v>
+        <v>0.01345507089218893</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1175691029390286</v>
+        <v>0.1035156612059661</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +595,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02301880827754807</v>
+        <v>0.008921043433614521</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002391493838836631</v>
+        <v>0.0007415144578270645</v>
       </c>
       <c r="D8" t="n">
-        <v>3.962271444860268</v>
+        <v>3.201424435774977</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00751086606513807</v>
+        <v>0.006206376460530291</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01830931334716203</v>
+        <v>0.00746629342454342</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02772830320793403</v>
+        <v>0.0103757934426858</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1173550092128218</v>
+        <v>0.1011521218367159</v>
       </c>
     </row>
     <row r="9">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02250608706600316</v>
+        <v>0.006025903808316439</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -631,7 +631,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.1168422880012769</v>
+        <v>0.09825698221141781</v>
       </c>
     </row>
     <row r="10">
@@ -641,15 +641,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02118775533242945</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>0.004586833873079899</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.000589702571148026</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4745646334839808</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004323239418186818</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.003424742761358057</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005748924984801827</v>
+      </c>
       <c r="H10" t="n">
-        <v>0.1155239562677032</v>
+        <v>0.09681791227618126</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +669,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03290212680018208</v>
+        <v>0.03107247162229704</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -667,7 +677,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1272383277354558</v>
+        <v>0.1233035500253984</v>
       </c>
     </row>
     <row r="12">
@@ -677,7 +687,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05522884478585557</v>
+        <v>0.05237653322518623</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -685,7 +695,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1495650457211293</v>
+        <v>0.1446076116282876</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +705,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06447114349309434</v>
+        <v>0.06222631872254442</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -703,7 +713,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1588073444283681</v>
+        <v>0.1544573971256458</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +723,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07477726774693204</v>
+        <v>0.07113874691315135</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -721,7 +731,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1691134686822058</v>
+        <v>0.1633698253162527</v>
       </c>
     </row>
     <row r="15">
@@ -731,7 +741,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08379256057805502</v>
+        <v>0.07936367246377027</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -739,7 +749,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1781287615133287</v>
+        <v>0.1715947508668716</v>
       </c>
     </row>
     <row r="16">
@@ -749,7 +759,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08547196115689153</v>
+        <v>0.08102572745594024</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -757,7 +767,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1798081620921653</v>
+        <v>0.1732568058590416</v>
       </c>
     </row>
     <row r="17">
@@ -767,7 +777,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08647074735830616</v>
+        <v>0.08327345366503502</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -775,7 +785,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1808069482935799</v>
+        <v>0.1755045320681364</v>
       </c>
     </row>
     <row r="18">
@@ -785,13 +795,23 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09433620093527373</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+        <v>-0.09223107840310137</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.01020592210718116</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-162032226114.6995</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.04379181626427429</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.1122971246838419</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.07216503212236026</v>
+      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -803,7 +823,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08991652577803222</v>
+        <v>0.08607245576703271</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -811,7 +831,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1842527267133059</v>
+        <v>0.1783035341701341</v>
       </c>
     </row>
     <row r="20">
@@ -821,7 +841,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09289966074206668</v>
+        <v>0.08791448888925449</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -829,7 +849,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1872358616773404</v>
+        <v>0.1801455672923559</v>
       </c>
     </row>
     <row r="21">
@@ -839,7 +859,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09690252412819515</v>
+        <v>0.09177433175374931</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -847,7 +867,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1912387250634689</v>
+        <v>0.1840054101568507</v>
       </c>
     </row>
     <row r="22">
@@ -857,7 +877,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1024495846870818</v>
+        <v>0.09710091686934544</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -865,7 +885,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1967857856223555</v>
+        <v>0.1893319952724468</v>
       </c>
     </row>
     <row r="23">
@@ -875,7 +895,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1066218907069758</v>
+        <v>0.1013351603267304</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -883,7 +903,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2009580916422495</v>
+        <v>0.1935662387298318</v>
       </c>
     </row>
     <row r="24">
@@ -893,25 +913,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1085586091990521</v>
+        <v>0.1044833765648279</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009358680330341335</v>
+        <v>0.008501324360828271</v>
       </c>
       <c r="D24" t="n">
-        <v>1902149455236.314</v>
+        <v>1882721529400.067</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05414537341580854</v>
+        <v>0.05136743793920907</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09013975715596718</v>
+        <v>0.08775863492024798</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1269774612421372</v>
+        <v>0.1212081182094077</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2028948101343259</v>
+        <v>0.1967144549679293</v>
       </c>
     </row>
     <row r="25">
@@ -921,25 +941,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1104705985162107</v>
+        <v>0.1054381458404927</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008747141398140494</v>
+        <v>0.008252791145076099</v>
       </c>
       <c r="D25" t="n">
-        <v>1181190483800.336</v>
+        <v>1167039415280.217</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05263272765295209</v>
+        <v>0.05197551312728708</v>
       </c>
       <c r="F25" t="n">
-        <v>0.093262762906375</v>
+        <v>0.08920310484825056</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1276784341260466</v>
+        <v>0.121673186832735</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2048067994514844</v>
+        <v>0.1976692242435941</v>
       </c>
     </row>
     <row r="26">
@@ -949,25 +969,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1132252464187097</v>
+        <v>0.1081925873086219</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008672562860085362</v>
+        <v>0.007902138586220643</v>
       </c>
       <c r="D26" t="n">
-        <v>1933663733577.018</v>
+        <v>1918013241331.514</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05438712232633147</v>
+        <v>0.05047104475177679</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09617233815460344</v>
+        <v>0.09265773545760324</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1302781546828162</v>
+        <v>0.1237274391596404</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2075614473539834</v>
+        <v>0.2004236657117233</v>
       </c>
     </row>
     <row r="27">
@@ -977,25 +997,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1154173152168604</v>
+        <v>0.1109566238630732</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008791485020300619</v>
+        <v>0.008077971760138388</v>
       </c>
       <c r="D27" t="n">
-        <v>21.55636275087432</v>
+        <v>21.59380031302495</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06375662027712767</v>
+        <v>0.05776205898742934</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09811727210318105</v>
+        <v>0.09506435939899466</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1327173583305405</v>
+        <v>0.1268488883271514</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2097535161521341</v>
+        <v>0.2031877022661745</v>
       </c>
     </row>
     <row r="28">
@@ -1005,25 +1025,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1168375201834414</v>
+        <v>0.1122265643320853</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008268580323377113</v>
+        <v>0.007509959791605961</v>
       </c>
       <c r="D28" t="n">
-        <v>1628309554361.351</v>
+        <v>1622464453432.309</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06936834759677808</v>
+        <v>0.06611310882803162</v>
       </c>
       <c r="F28" t="n">
-        <v>0.100572693624265</v>
+        <v>0.09745845195652657</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1331023467426175</v>
+        <v>0.1269946767076442</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2111737211187151</v>
+        <v>0.2044576427351867</v>
       </c>
     </row>
     <row r="29">
@@ -1033,25 +1053,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02085980600167717</v>
+        <v>0.005327726239293104</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002164877931745044</v>
+        <v>0.0006422273029637292</v>
       </c>
       <c r="D29" t="n">
-        <v>2.025833849636871</v>
+        <v>0.8842422119557817</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01876538776019561</v>
+        <v>0.01721611072308222</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0165941283720794</v>
+        <v>0.004067146639627361</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02512548363127512</v>
+        <v>0.006588305838958811</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1151960069369509</v>
+        <v>0.09755880464239447</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year8final.xlsx
+++ b/hourly datasets/cap_gen_year8final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2216105754039258</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09223107840310137</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.08926501273002238</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09877494058704042</v>
+        <v>0.3737733625728674</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1910060189901418</v>
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.241427799898964</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08041191303485394</v>
+        <v>0.3702798474634793</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1726429914379553</v>
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2379342847895759</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05721070602727303</v>
+        <v>0.3719743609687588</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1494417844303744</v>
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2396287982948554</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +566,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03592349993804324</v>
+        <v>0.3690890848125828</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +574,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1281545783411446</v>
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2367435221386794</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +587,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01128458280286472</v>
+        <v>0.407352325632561</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001106705717181267</v>
+        <v>0.006520463981933565</v>
       </c>
       <c r="D7" t="n">
-        <v>2.359853202451919</v>
+        <v>11.2187154088472</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01112575066180846</v>
+        <v>0.01329566159815926</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009114094713539968</v>
+        <v>0.05049710699226249</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01345507089218893</v>
+        <v>0.07610299147717198</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1035156612059661</v>
+        <v>80</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2750067629586576</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +618,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008921043433614521</v>
+        <v>0.4914977666985169</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007415144578270645</v>
+        <v>0.001637540366989129</v>
       </c>
       <c r="D8" t="n">
-        <v>3.201424435774977</v>
+        <v>101.2462475787165</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006206376460530291</v>
+        <v>0.008030528248882516</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00746629342454342</v>
+        <v>0.07901386342155117</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0103757934426858</v>
+        <v>0.08544162862127373</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1011521218367159</v>
+        <v>111</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3591522040246135</v>
       </c>
     </row>
     <row r="9">
@@ -623,7 +649,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006025903808316439</v>
+        <v>0.5078786671319064</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -631,7 +657,10 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.09825698221141781</v>
+        <v>140</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.375533104458003</v>
       </c>
     </row>
     <row r="10">
@@ -641,25 +670,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004586833873079899</v>
+        <v>0.4785646983078523</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000589702571148026</v>
+        <v>0.001740246962833317</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4745646334839808</v>
+        <v>-10.42171800283082</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004323239418186818</v>
+        <v>0.005581965331302586</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003424742761358057</v>
+        <v>-0.007298012984870866</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005748924984801827</v>
+        <v>-0.000460355036896444</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09681791227618126</v>
+        <v>140</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3462191356339489</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +701,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03107247162229704</v>
+        <v>0.263939614032781</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -677,7 +709,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1233035500253984</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1315940513588776</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +722,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05237653322518623</v>
+        <v>0.2901814524341553</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -695,7 +730,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1446076116282876</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1578358897602519</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06222631872254442</v>
+        <v>0.3039020173817837</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -713,7 +751,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1544573971256458</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1715564547078803</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +764,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07113874691315135</v>
+        <v>0.3127369846957586</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -731,7 +772,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1633698253162527</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1803914220218552</v>
       </c>
     </row>
     <row r="15">
@@ -741,7 +785,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07936367246377027</v>
+        <v>0.3224403286863626</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -749,7 +793,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1715947508668716</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1900947660124592</v>
       </c>
     </row>
     <row r="16">
@@ -759,7 +806,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08102572745594024</v>
+        <v>0.3266991724185173</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -767,7 +814,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1732568058590416</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1943536097446139</v>
       </c>
     </row>
     <row r="17">
@@ -777,7 +827,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08327345366503502</v>
+        <v>0.3304139950613826</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -785,7 +835,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1755045320681364</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1980684323874792</v>
       </c>
     </row>
     <row r="18">
@@ -795,24 +848,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09223107840310137</v>
+        <v>0.1323455626739034</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01020592210718116</v>
+        <v>0.01006834292852203</v>
       </c>
       <c r="D18" t="n">
-        <v>-162032226114.6995</v>
+        <v>-162013477506.4435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04379181626427429</v>
+        <v>0.04299879041268692</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1122971246838419</v>
+        <v>-0.1114308990557917</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07216503212236026</v>
+        <v>-0.07184049152419672</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -823,7 +879,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08607245576703271</v>
+        <v>0.3329995440119051</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -831,7 +887,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1783035341701341</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2006539813380017</v>
       </c>
     </row>
     <row r="20">
@@ -841,7 +900,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08791448888925449</v>
+        <v>0.3366886717705399</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -849,7 +908,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1801455672923559</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2043431090966365</v>
       </c>
     </row>
     <row r="21">
@@ -859,7 +921,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09177433175374931</v>
+        <v>0.3408779176578723</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -867,7 +929,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1840054101568507</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2085323549839689</v>
       </c>
     </row>
     <row r="22">
@@ -877,7 +942,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09710091686934544</v>
+        <v>0.3449866671280248</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -885,7 +950,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1893319952724468</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2126411044541214</v>
       </c>
     </row>
     <row r="23">
@@ -895,7 +963,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1013351603267304</v>
+        <v>0.3518532264595381</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -903,7 +971,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1935662387298318</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2195076637856347</v>
       </c>
     </row>
     <row r="24">
@@ -913,25 +984,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1044833765648279</v>
+        <v>0.3577769368304846</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008501324360828271</v>
+        <v>0.008457231847852279</v>
       </c>
       <c r="D24" t="n">
-        <v>1882721529400.067</v>
+        <v>1882442340750.692</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05136743793920907</v>
+        <v>0.05133305766538503</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08775863492024798</v>
+        <v>0.08736193609716195</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1212081182094077</v>
+        <v>0.1206382204312876</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1967144549679293</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2254313741565812</v>
       </c>
     </row>
     <row r="25">
@@ -941,25 +1015,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1054381458404927</v>
+        <v>0.3609347964197717</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008252791145076099</v>
+        <v>0.008203858960231377</v>
       </c>
       <c r="D25" t="n">
-        <v>1167039415280.217</v>
+        <v>1166836010531.269</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05197551312728708</v>
+        <v>0.05185355529566001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08920310484825056</v>
+        <v>0.08875863714639431</v>
       </c>
       <c r="G25" t="n">
-        <v>0.121673186832735</v>
+        <v>0.121036379292139</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1976692242435941</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2285892337458683</v>
       </c>
     </row>
     <row r="26">
@@ -969,25 +1046,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1081925873086219</v>
+        <v>0.3657002682106079</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007902138586220643</v>
+        <v>0.00784141123884044</v>
       </c>
       <c r="D26" t="n">
-        <v>1918013241331.514</v>
+        <v>1917595957012.06</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05047104475177679</v>
+        <v>0.05039727443938379</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09265773545760324</v>
+        <v>0.09212109957773312</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1237274391596404</v>
+        <v>0.1229521634468636</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2004236657117233</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2333547055367045</v>
       </c>
     </row>
     <row r="27">
@@ -997,25 +1077,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1109566238630732</v>
+        <v>0.3739261900871004</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008077971760138388</v>
+        <v>0.0082159423535403</v>
       </c>
       <c r="D27" t="n">
-        <v>21.59380031302495</v>
+        <v>21.79612751499836</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05776205898742934</v>
+        <v>0.05896788763092643</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09506435939899466</v>
+        <v>0.09580866385004391</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1268488883271514</v>
+        <v>0.1281371144824963</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2031877022661745</v>
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.241580627413197</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1108,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1122265643320853</v>
+        <v>0.3651141447454164</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007509959791605961</v>
+        <v>0.007283497230487115</v>
       </c>
       <c r="D28" t="n">
-        <v>1622464453432.309</v>
+        <v>1622004897070.896</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06611310882803162</v>
+        <v>0.06582788465363336</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09745845195652657</v>
+        <v>0.09500235029440292</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1269946767076442</v>
+        <v>0.1236462438085193</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2044576427351867</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.232768582071513</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1139,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005327726239293104</v>
+        <v>0.3335382188439759</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0006422273029637292</v>
+        <v>0.001902791683995916</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8842422119557817</v>
+        <v>1.445379305527401</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01721611072308222</v>
+        <v>0.6312119882926159</v>
       </c>
       <c r="F29" t="n">
-        <v>0.004067146639627361</v>
+        <v>0.003586932449018486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006588305838958811</v>
+        <v>0.01105634752521488</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09755880464239447</v>
+        <v>89</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2011926561700725</v>
       </c>
     </row>
   </sheetData>
